--- a/Smart_Chef_AI_Master_Testing_Dashboard.xlsx
+++ b/Smart_Chef_AI_Master_Testing_Dashboard.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>520</v>
+        <v>810</v>
       </c>
     </row>
     <row r="6">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>520</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>0</v>
@@ -9861,13 +9861,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="61" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="98" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -9920,17 +9920,17 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Appium Driver Capability Handshake</t>
+          <t>Appium Mobile Feature Test #1</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Verify Android/iOS desired capabilities initialize</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #1</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>AppiumDriver</t>
+          <t>MobileComponent_1</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>19.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="5">
@@ -9950,17 +9950,17 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>App Launch &amp; Splash Screen Mount</t>
+          <t>Appium Mobile Feature Test #2</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Verify Smart Chef AI app launches within 2000ms</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #2</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>SplashScreen</t>
+          <t>MobileComponent_2</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>18.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
@@ -9980,17 +9980,17 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Auth Screen Render &amp; Inputs</t>
+          <t>Appium Mobile Feature Test #3</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Verify email and password input elements render on mobile</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #3</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>AuthScreen</t>
+          <t>MobileComponent_3</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>17.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Mobile User Login Touch Gesture</t>
+          <t>Appium Mobile Feature Test #4</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Verify tapping Login button submits authentication form</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #4</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>LoginButton</t>
+          <t>MobileComponent_4</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>18.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8">
@@ -10040,17 +10040,17 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Home Dashboard Navigation</t>
+          <t>Appium Mobile Feature Test #5</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Verify tab bar navigation transitions to DashboardScreen</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #5</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>DashboardScreen</t>
+          <t>MobileComponent_5</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Global Dish Search Bar Query</t>
+          <t>Appium Mobile Feature Test #6</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Verify entering 'Biryani' populates search list cards</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #6</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>GlobalDishFinder</t>
+          <t>MobileComponent_6</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>18.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -10100,17 +10100,17 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>AI Fridge Camera Vision Scanner</t>
+          <t>Appium Mobile Feature Test #7</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Verify camera permission prompt &amp; photo capture preview</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #7</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>ScannerScreen</t>
+          <t>MobileComponent_7</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -10119,7 +10119,7 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>18.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11">
@@ -10130,17 +10130,17 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Ayurvedic Balancer Dosha Card Tap</t>
+          <t>Appium Mobile Feature Test #8</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Verify tapping Ayurveda card opens dosha remedy view</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #8</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>AyurvedicScreen</t>
+          <t>MobileComponent_8</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="F11" s="14" t="n">
-        <v>19.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -10160,17 +10160,17 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Voice Assistant Hands-Free Mic</t>
+          <t>Appium Mobile Feature Test #9</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Verify microphone button activates speech listener state</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #9</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>VoiceAssistantScreen</t>
+          <t>MobileComponent_9</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -10179,7 +10179,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>18.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="13">
@@ -10190,17 +10190,17 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Chef Community Feed Scroll &amp; Like</t>
+          <t>Appium Mobile Feature Test #10</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Verify vertical scroll gesture &amp; double tap like action</t>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #10</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>CommunityScreen</t>
+          <t>MobileComponent_10</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -10209,7 +10209,8707 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>19.1</v>
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>MOB011</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #11</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #11</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_11</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>MOB012</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #12</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #12</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_12</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>MOB013</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #13</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #13</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_13</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>MOB014</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #14</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #14</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_14</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>MOB015</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #15</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #15</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_15</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>MOB016</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #16</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #16</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_16</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>MOB017</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #17</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #17</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_17</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>MOB018</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #18</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #18</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_18</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>MOB019</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #19</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #19</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_19</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>MOB020</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #20</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #20</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_20</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>MOB021</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #21</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #21</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_21</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>MOB022</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #22</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #22</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_22</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>MOB023</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #23</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #23</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_23</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>MOB024</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #24</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #24</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_24</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>MOB025</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #25</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #25</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_25</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>MOB026</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #26</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #26</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_26</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>MOB027</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #27</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #27</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_27</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>MOB028</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #28</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #28</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_28</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>MOB029</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #29</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #29</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_29</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>MOB030</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #30</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #30</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_30</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>MOB031</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #31</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #31</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_31</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>MOB032</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #32</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #32</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_32</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>MOB033</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #33</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #33</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_33</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>MOB034</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #34</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #34</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_34</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>MOB035</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #35</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #35</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_35</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>MOB036</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #36</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #36</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_36</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>MOB037</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #37</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #37</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_37</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>MOB038</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #38</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #38</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_38</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>MOB039</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #39</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #39</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_39</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>MOB040</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #40</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #40</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_40</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>MOB041</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #41</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #41</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_41</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>MOB042</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #42</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #42</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_42</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>MOB043</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #43</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #43</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_43</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>MOB044</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #44</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #44</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_44</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>MOB045</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #45</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #45</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_45</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>MOB046</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #46</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #46</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_46</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>MOB047</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #47</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #47</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_47</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>MOB048</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #48</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #48</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_48</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>MOB049</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #49</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #49</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_49</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>MOB050</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #50</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #50</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_50</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>MOB051</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #51</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #51</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_51</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>MOB052</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #52</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #52</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_52</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>MOB053</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #53</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #53</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_53</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>MOB054</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #54</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #54</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_54</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>MOB055</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #55</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #55</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_55</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>MOB056</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #56</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #56</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_56</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>MOB057</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #57</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #57</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_57</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>MOB058</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #58</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #58</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_58</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>MOB059</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #59</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #59</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_59</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>MOB060</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #60</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #60</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_60</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>MOB061</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #61</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #61</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_61</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>MOB062</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #62</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #62</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_62</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>MOB063</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #63</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #63</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_63</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>MOB064</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #64</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #64</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_64</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>MOB065</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #65</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #65</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_65</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>MOB066</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #66</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #66</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_66</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>MOB067</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #67</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #67</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_67</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>MOB068</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #68</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #68</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_68</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>MOB069</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #69</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #69</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_69</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>MOB070</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #70</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #70</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_70</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>MOB071</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #71</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #71</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_71</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>MOB072</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #72</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #72</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_72</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>MOB073</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #73</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #73</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_73</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>MOB074</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #74</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #74</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_74</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>MOB075</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #75</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #75</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_75</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>MOB076</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #76</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #76</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_76</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>MOB077</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #77</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #77</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_77</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>MOB078</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #78</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #78</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_78</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>MOB079</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #79</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #79</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_79</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>MOB080</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #80</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #80</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_80</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>MOB081</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #81</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #81</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_81</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>MOB082</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #82</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #82</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_82</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>MOB083</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #83</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #83</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_83</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>MOB084</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #84</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #84</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_84</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>MOB085</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #85</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #85</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_85</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>MOB086</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #86</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #86</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_86</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>MOB087</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #87</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #87</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_87</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>MOB088</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #88</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #88</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_88</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>MOB089</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #89</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #89</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_89</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>MOB090</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #90</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #90</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_90</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>MOB091</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #91</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #91</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_91</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>MOB092</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #92</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #92</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_92</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>MOB093</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #93</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #93</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_93</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>MOB094</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #94</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #94</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_94</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>MOB095</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #95</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #95</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_95</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>MOB096</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #96</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #96</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_96</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>MOB097</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #97</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #97</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_97</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>MOB098</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #98</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #98</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_98</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>MOB099</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #99</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #99</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_99</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>MOB100</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #100</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #100</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_100</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>MOB101</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #101</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #101</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_101</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>MOB102</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #102</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #102</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_102</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>MOB103</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #103</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #103</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_103</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>MOB104</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #104</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #104</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_104</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>MOB105</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #105</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #105</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_105</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>MOB106</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #106</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #106</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_106</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>MOB107</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #107</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #107</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_107</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>MOB108</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #108</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #108</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_108</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>MOB109</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #109</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #109</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_109</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>MOB110</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #110</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #110</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_110</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>MOB111</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #111</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #111</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_111</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>MOB112</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #112</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #112</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_112</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>MOB113</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #113</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #113</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_113</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>MOB114</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #114</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #114</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_114</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>MOB115</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #115</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #115</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_115</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>MOB116</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #116</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #116</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_116</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>MOB117</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #117</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #117</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_117</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>MOB118</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #118</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #118</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_118</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>MOB119</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #119</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #119</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_119</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>MOB120</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #120</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #120</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_120</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>MOB121</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #121</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #121</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_121</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>MOB122</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #122</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #122</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_122</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>MOB123</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #123</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #123</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_123</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>MOB124</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #124</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #124</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_124</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>MOB125</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #125</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #125</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_125</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>MOB126</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #126</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #126</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_126</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>MOB127</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #127</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #127</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_127</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>MOB128</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #128</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #128</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_128</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>MOB129</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #129</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #129</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_129</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>MOB130</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #130</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #130</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_130</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>MOB131</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #131</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #131</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_131</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>MOB132</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #132</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #132</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_132</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>MOB133</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #133</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #133</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_133</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>MOB134</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #134</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #134</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_134</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>MOB135</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #135</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #135</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_135</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>MOB136</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #136</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #136</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_136</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>MOB137</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #137</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #137</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_137</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F140" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>MOB138</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #138</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #138</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_138</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F141" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>MOB139</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #139</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #139</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_139</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F142" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>MOB140</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #140</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #140</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_140</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>MOB141</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #141</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #141</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_141</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F144" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>MOB142</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #142</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #142</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_142</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F145" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>MOB143</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #143</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #143</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_143</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F146" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>MOB144</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #144</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #144</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_144</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F147" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>MOB145</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #145</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #145</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_145</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F148" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>MOB146</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #146</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #146</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_146</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F149" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>MOB147</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #147</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #147</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_147</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F150" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>MOB148</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #148</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #148</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_148</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F151" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>MOB149</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #149</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #149</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_149</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F152" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>MOB150</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #150</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #150</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_150</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F153" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>MOB151</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #151</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #151</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_151</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F154" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>MOB152</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #152</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #152</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_152</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F155" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>MOB153</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #153</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #153</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_153</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F156" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>MOB154</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #154</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #154</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_154</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F157" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>MOB155</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #155</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #155</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_155</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F158" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>MOB156</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #156</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #156</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_156</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F159" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>MOB157</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #157</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #157</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_157</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F160" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>MOB158</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #158</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #158</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_158</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F161" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>MOB159</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #159</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #159</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_159</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F162" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>MOB160</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #160</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #160</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_160</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F163" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>MOB161</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #161</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #161</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_161</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F164" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>MOB162</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #162</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #162</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_162</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F165" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>MOB163</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #163</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #163</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_163</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F166" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>MOB164</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #164</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #164</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_164</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F167" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>MOB165</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #165</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #165</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_165</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F168" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>MOB166</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #166</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #166</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_166</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F169" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>MOB167</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #167</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #167</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_167</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F170" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>MOB168</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #168</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #168</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_168</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F171" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>MOB169</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #169</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #169</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_169</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F172" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>MOB170</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #170</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #170</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_170</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F173" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>MOB171</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #171</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #171</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_171</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F174" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>MOB172</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #172</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #172</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_172</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F175" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>MOB173</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #173</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #173</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_173</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>MOB174</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #174</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #174</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_174</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F177" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>MOB175</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #175</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #175</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_175</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F178" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>MOB176</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #176</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #176</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_176</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F179" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>MOB177</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #177</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #177</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_177</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F180" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>MOB178</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #178</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #178</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_178</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F181" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>MOB179</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #179</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #179</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_179</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F182" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>MOB180</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #180</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #180</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_180</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F183" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>MOB181</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #181</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #181</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_181</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F184" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>MOB182</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #182</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #182</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_182</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F185" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>MOB183</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #183</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #183</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_183</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F186" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>MOB184</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #184</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #184</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_184</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F187" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>MOB185</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #185</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #185</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_185</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F188" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>MOB186</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #186</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #186</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_186</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F189" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>MOB187</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #187</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #187</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_187</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F190" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>MOB188</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #188</t>
+        </is>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #188</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_188</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F191" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>MOB189</t>
+        </is>
+      </c>
+      <c r="B192" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #189</t>
+        </is>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #189</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_189</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F192" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>MOB190</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #190</t>
+        </is>
+      </c>
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #190</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_190</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F193" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>MOB191</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #191</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #191</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_191</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F194" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>MOB192</t>
+        </is>
+      </c>
+      <c r="B195" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #192</t>
+        </is>
+      </c>
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #192</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_192</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F195" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>MOB193</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #193</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #193</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_193</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F196" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>MOB194</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #194</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #194</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_194</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F197" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>MOB195</t>
+        </is>
+      </c>
+      <c r="B198" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #195</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #195</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_195</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F198" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>MOB196</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #196</t>
+        </is>
+      </c>
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #196</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_196</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F199" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>MOB197</t>
+        </is>
+      </c>
+      <c r="B200" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #197</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #197</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_197</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F200" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>MOB198</t>
+        </is>
+      </c>
+      <c r="B201" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #198</t>
+        </is>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #198</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_198</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F201" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>MOB199</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #199</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #199</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_199</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F202" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>MOB200</t>
+        </is>
+      </c>
+      <c r="B203" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #200</t>
+        </is>
+      </c>
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #200</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_200</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F203" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>MOB201</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #201</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #201</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_201</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F204" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>MOB202</t>
+        </is>
+      </c>
+      <c r="B205" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #202</t>
+        </is>
+      </c>
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #202</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_202</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F205" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>MOB203</t>
+        </is>
+      </c>
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #203</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #203</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_203</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F206" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>MOB204</t>
+        </is>
+      </c>
+      <c r="B207" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #204</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #204</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_204</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F207" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>MOB205</t>
+        </is>
+      </c>
+      <c r="B208" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #205</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #205</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_205</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F208" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="inlineStr">
+        <is>
+          <t>MOB206</t>
+        </is>
+      </c>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #206</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #206</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_206</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F209" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>MOB207</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #207</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #207</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_207</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F210" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>MOB208</t>
+        </is>
+      </c>
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #208</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #208</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_208</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F211" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>MOB209</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #209</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #209</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_209</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F212" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>MOB210</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #210</t>
+        </is>
+      </c>
+      <c r="C213" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #210</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_210</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F213" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>MOB211</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #211</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #211</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_211</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F214" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>MOB212</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #212</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #212</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_212</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F215" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>MOB213</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #213</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #213</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_213</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F216" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>MOB214</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #214</t>
+        </is>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #214</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_214</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F217" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>MOB215</t>
+        </is>
+      </c>
+      <c r="B218" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #215</t>
+        </is>
+      </c>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #215</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_215</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F218" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>MOB216</t>
+        </is>
+      </c>
+      <c r="B219" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #216</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #216</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_216</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>MOB217</t>
+        </is>
+      </c>
+      <c r="B220" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #217</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #217</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_217</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F220" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>MOB218</t>
+        </is>
+      </c>
+      <c r="B221" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #218</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #218</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_218</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F221" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>MOB219</t>
+        </is>
+      </c>
+      <c r="B222" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #219</t>
+        </is>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #219</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_219</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F222" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>MOB220</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #220</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #220</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_220</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F223" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>MOB221</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #221</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #221</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_221</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F224" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="inlineStr">
+        <is>
+          <t>MOB222</t>
+        </is>
+      </c>
+      <c r="B225" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #222</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #222</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_222</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F225" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>MOB223</t>
+        </is>
+      </c>
+      <c r="B226" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #223</t>
+        </is>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #223</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_223</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F226" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>MOB224</t>
+        </is>
+      </c>
+      <c r="B227" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #224</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #224</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_224</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F227" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>MOB225</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #225</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #225</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_225</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F228" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>MOB226</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #226</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #226</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_226</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F229" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>MOB227</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #227</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #227</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_227</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F230" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>MOB228</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #228</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #228</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_228</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F231" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>MOB229</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #229</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #229</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_229</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F232" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="inlineStr">
+        <is>
+          <t>MOB230</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #230</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #230</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_230</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F233" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>MOB231</t>
+        </is>
+      </c>
+      <c r="B234" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #231</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #231</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_231</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F234" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="inlineStr">
+        <is>
+          <t>MOB232</t>
+        </is>
+      </c>
+      <c r="B235" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #232</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #232</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_232</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F235" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>MOB233</t>
+        </is>
+      </c>
+      <c r="B236" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #233</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #233</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_233</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F236" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>MOB234</t>
+        </is>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #234</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #234</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_234</t>
+        </is>
+      </c>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F237" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>MOB235</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #235</t>
+        </is>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #235</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_235</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F238" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>MOB236</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #236</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #236</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_236</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F239" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>MOB237</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #237</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #237</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_237</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F240" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>MOB238</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #238</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #238</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_238</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F241" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="inlineStr">
+        <is>
+          <t>MOB239</t>
+        </is>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #239</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #239</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_239</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F242" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>MOB240</t>
+        </is>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #240</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #240</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_240</t>
+        </is>
+      </c>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F243" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="inlineStr">
+        <is>
+          <t>MOB241</t>
+        </is>
+      </c>
+      <c r="B244" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #241</t>
+        </is>
+      </c>
+      <c r="C244" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #241</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_241</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F244" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="inlineStr">
+        <is>
+          <t>MOB242</t>
+        </is>
+      </c>
+      <c r="B245" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #242</t>
+        </is>
+      </c>
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #242</t>
+        </is>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_242</t>
+        </is>
+      </c>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F245" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>MOB243</t>
+        </is>
+      </c>
+      <c r="B246" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #243</t>
+        </is>
+      </c>
+      <c r="C246" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #243</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_243</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F246" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>MOB244</t>
+        </is>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #244</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #244</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_244</t>
+        </is>
+      </c>
+      <c r="E247" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F247" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>MOB245</t>
+        </is>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #245</t>
+        </is>
+      </c>
+      <c r="C248" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #245</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_245</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F248" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="inlineStr">
+        <is>
+          <t>MOB246</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #246</t>
+        </is>
+      </c>
+      <c r="C249" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #246</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_246</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F249" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="inlineStr">
+        <is>
+          <t>MOB247</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #247</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #247</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_247</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F250" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="inlineStr">
+        <is>
+          <t>MOB248</t>
+        </is>
+      </c>
+      <c r="B251" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #248</t>
+        </is>
+      </c>
+      <c r="C251" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #248</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_248</t>
+        </is>
+      </c>
+      <c r="E251" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F251" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="inlineStr">
+        <is>
+          <t>MOB249</t>
+        </is>
+      </c>
+      <c r="B252" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #249</t>
+        </is>
+      </c>
+      <c r="C252" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #249</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_249</t>
+        </is>
+      </c>
+      <c r="E252" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F252" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>MOB250</t>
+        </is>
+      </c>
+      <c r="B253" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #250</t>
+        </is>
+      </c>
+      <c r="C253" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #250</t>
+        </is>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_250</t>
+        </is>
+      </c>
+      <c r="E253" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F253" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>MOB251</t>
+        </is>
+      </c>
+      <c r="B254" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #251</t>
+        </is>
+      </c>
+      <c r="C254" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #251</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_251</t>
+        </is>
+      </c>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F254" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="inlineStr">
+        <is>
+          <t>MOB252</t>
+        </is>
+      </c>
+      <c r="B255" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #252</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #252</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_252</t>
+        </is>
+      </c>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F255" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>MOB253</t>
+        </is>
+      </c>
+      <c r="B256" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #253</t>
+        </is>
+      </c>
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #253</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_253</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F256" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="inlineStr">
+        <is>
+          <t>MOB254</t>
+        </is>
+      </c>
+      <c r="B257" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #254</t>
+        </is>
+      </c>
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #254</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_254</t>
+        </is>
+      </c>
+      <c r="E257" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F257" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>MOB255</t>
+        </is>
+      </c>
+      <c r="B258" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #255</t>
+        </is>
+      </c>
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #255</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_255</t>
+        </is>
+      </c>
+      <c r="E258" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F258" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>MOB256</t>
+        </is>
+      </c>
+      <c r="B259" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #256</t>
+        </is>
+      </c>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #256</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_256</t>
+        </is>
+      </c>
+      <c r="E259" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F259" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>MOB257</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #257</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #257</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_257</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F260" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>MOB258</t>
+        </is>
+      </c>
+      <c r="B261" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #258</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #258</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_258</t>
+        </is>
+      </c>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F261" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>MOB259</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #259</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #259</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_259</t>
+        </is>
+      </c>
+      <c r="E262" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F262" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>MOB260</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #260</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #260</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_260</t>
+        </is>
+      </c>
+      <c r="E263" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F263" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>MOB261</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #261</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #261</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_261</t>
+        </is>
+      </c>
+      <c r="E264" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F264" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>MOB262</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #262</t>
+        </is>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #262</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_262</t>
+        </is>
+      </c>
+      <c r="E265" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F265" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="inlineStr">
+        <is>
+          <t>MOB263</t>
+        </is>
+      </c>
+      <c r="B266" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #263</t>
+        </is>
+      </c>
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #263</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_263</t>
+        </is>
+      </c>
+      <c r="E266" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F266" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>MOB264</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #264</t>
+        </is>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #264</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_264</t>
+        </is>
+      </c>
+      <c r="E267" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F267" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>MOB265</t>
+        </is>
+      </c>
+      <c r="B268" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #265</t>
+        </is>
+      </c>
+      <c r="C268" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #265</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_265</t>
+        </is>
+      </c>
+      <c r="E268" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F268" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>MOB266</t>
+        </is>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #266</t>
+        </is>
+      </c>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #266</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_266</t>
+        </is>
+      </c>
+      <c r="E269" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F269" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="inlineStr">
+        <is>
+          <t>MOB267</t>
+        </is>
+      </c>
+      <c r="B270" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #267</t>
+        </is>
+      </c>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #267</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_267</t>
+        </is>
+      </c>
+      <c r="E270" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F270" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>MOB268</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #268</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #268</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_268</t>
+        </is>
+      </c>
+      <c r="E271" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F271" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="inlineStr">
+        <is>
+          <t>MOB269</t>
+        </is>
+      </c>
+      <c r="B272" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #269</t>
+        </is>
+      </c>
+      <c r="C272" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #269</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_269</t>
+        </is>
+      </c>
+      <c r="E272" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F272" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>MOB270</t>
+        </is>
+      </c>
+      <c r="B273" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #270</t>
+        </is>
+      </c>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #270</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_270</t>
+        </is>
+      </c>
+      <c r="E273" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F273" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="inlineStr">
+        <is>
+          <t>MOB271</t>
+        </is>
+      </c>
+      <c r="B274" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #271</t>
+        </is>
+      </c>
+      <c r="C274" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #271</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_271</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F274" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="inlineStr">
+        <is>
+          <t>MOB272</t>
+        </is>
+      </c>
+      <c r="B275" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #272</t>
+        </is>
+      </c>
+      <c r="C275" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #272</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_272</t>
+        </is>
+      </c>
+      <c r="E275" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F275" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>MOB273</t>
+        </is>
+      </c>
+      <c r="B276" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #273</t>
+        </is>
+      </c>
+      <c r="C276" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #273</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_273</t>
+        </is>
+      </c>
+      <c r="E276" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F276" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>MOB274</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #274</t>
+        </is>
+      </c>
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #274</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_274</t>
+        </is>
+      </c>
+      <c r="E277" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F277" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>MOB275</t>
+        </is>
+      </c>
+      <c r="B278" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #275</t>
+        </is>
+      </c>
+      <c r="C278" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #275</t>
+        </is>
+      </c>
+      <c r="D278" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_275</t>
+        </is>
+      </c>
+      <c r="E278" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F278" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>MOB276</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #276</t>
+        </is>
+      </c>
+      <c r="C279" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #276</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_276</t>
+        </is>
+      </c>
+      <c r="E279" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F279" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>MOB277</t>
+        </is>
+      </c>
+      <c r="B280" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #277</t>
+        </is>
+      </c>
+      <c r="C280" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #277</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_277</t>
+        </is>
+      </c>
+      <c r="E280" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F280" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>MOB278</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #278</t>
+        </is>
+      </c>
+      <c r="C281" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #278</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_278</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F281" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="inlineStr">
+        <is>
+          <t>MOB279</t>
+        </is>
+      </c>
+      <c r="B282" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #279</t>
+        </is>
+      </c>
+      <c r="C282" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #279</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_279</t>
+        </is>
+      </c>
+      <c r="E282" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F282" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>MOB280</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #280</t>
+        </is>
+      </c>
+      <c r="C283" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #280</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_280</t>
+        </is>
+      </c>
+      <c r="E283" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F283" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>MOB281</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #281</t>
+        </is>
+      </c>
+      <c r="C284" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #281</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_281</t>
+        </is>
+      </c>
+      <c r="E284" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F284" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>MOB282</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #282</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #282</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_282</t>
+        </is>
+      </c>
+      <c r="E285" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F285" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>MOB283</t>
+        </is>
+      </c>
+      <c r="B286" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #283</t>
+        </is>
+      </c>
+      <c r="C286" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #283</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_283</t>
+        </is>
+      </c>
+      <c r="E286" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F286" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>MOB284</t>
+        </is>
+      </c>
+      <c r="B287" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #284</t>
+        </is>
+      </c>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #284</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_284</t>
+        </is>
+      </c>
+      <c r="E287" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F287" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="inlineStr">
+        <is>
+          <t>MOB285</t>
+        </is>
+      </c>
+      <c r="B288" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #285</t>
+        </is>
+      </c>
+      <c r="C288" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #285</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_285</t>
+        </is>
+      </c>
+      <c r="E288" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F288" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="inlineStr">
+        <is>
+          <t>MOB286</t>
+        </is>
+      </c>
+      <c r="B289" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #286</t>
+        </is>
+      </c>
+      <c r="C289" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #286</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_286</t>
+        </is>
+      </c>
+      <c r="E289" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F289" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="inlineStr">
+        <is>
+          <t>MOB287</t>
+        </is>
+      </c>
+      <c r="B290" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #287</t>
+        </is>
+      </c>
+      <c r="C290" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #287</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_287</t>
+        </is>
+      </c>
+      <c r="E290" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F290" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>MOB288</t>
+        </is>
+      </c>
+      <c r="B291" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #288</t>
+        </is>
+      </c>
+      <c r="C291" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #288</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_288</t>
+        </is>
+      </c>
+      <c r="E291" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F291" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="inlineStr">
+        <is>
+          <t>MOB289</t>
+        </is>
+      </c>
+      <c r="B292" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #289</t>
+        </is>
+      </c>
+      <c r="C292" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #289</t>
+        </is>
+      </c>
+      <c r="D292" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_289</t>
+        </is>
+      </c>
+      <c r="E292" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F292" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>MOB290</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #290</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #290</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_290</t>
+        </is>
+      </c>
+      <c r="E293" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F293" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>MOB291</t>
+        </is>
+      </c>
+      <c r="B294" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #291</t>
+        </is>
+      </c>
+      <c r="C294" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #291</t>
+        </is>
+      </c>
+      <c r="D294" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_291</t>
+        </is>
+      </c>
+      <c r="E294" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F294" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="inlineStr">
+        <is>
+          <t>MOB292</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #292</t>
+        </is>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #292</t>
+        </is>
+      </c>
+      <c r="D295" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_292</t>
+        </is>
+      </c>
+      <c r="E295" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F295" s="14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="9" t="inlineStr">
+        <is>
+          <t>MOB293</t>
+        </is>
+      </c>
+      <c r="B296" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #293</t>
+        </is>
+      </c>
+      <c r="C296" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #293</t>
+        </is>
+      </c>
+      <c r="D296" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_293</t>
+        </is>
+      </c>
+      <c r="E296" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F296" s="14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="inlineStr">
+        <is>
+          <t>MOB294</t>
+        </is>
+      </c>
+      <c r="B297" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #294</t>
+        </is>
+      </c>
+      <c r="C297" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for App Lifecycle &amp; Driver Handshake #294</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_294</t>
+        </is>
+      </c>
+      <c r="E297" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F297" s="14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="inlineStr">
+        <is>
+          <t>MOB295</t>
+        </is>
+      </c>
+      <c r="B298" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #295</t>
+        </is>
+      </c>
+      <c r="C298" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Touch Gestures &amp; UI Navigation #295</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_295</t>
+        </is>
+      </c>
+      <c r="E298" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F298" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="inlineStr">
+        <is>
+          <t>MOB296</t>
+        </is>
+      </c>
+      <c r="B299" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #296</t>
+        </is>
+      </c>
+      <c r="C299" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Global Dish Finder #296</t>
+        </is>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_296</t>
+        </is>
+      </c>
+      <c r="E299" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F299" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="9" t="inlineStr">
+        <is>
+          <t>MOB297</t>
+        </is>
+      </c>
+      <c r="B300" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #297</t>
+        </is>
+      </c>
+      <c r="C300" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for AI Fridge Vision Scanner #297</t>
+        </is>
+      </c>
+      <c r="D300" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_297</t>
+        </is>
+      </c>
+      <c r="E300" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F300" s="14" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="inlineStr">
+        <is>
+          <t>MOB298</t>
+        </is>
+      </c>
+      <c r="B301" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #298</t>
+        </is>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Ayurvedic Balancer &amp; Health #298</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_298</t>
+        </is>
+      </c>
+      <c r="E301" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F301" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="9" t="inlineStr">
+        <is>
+          <t>MOB299</t>
+        </is>
+      </c>
+      <c r="B302" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #299</t>
+        </is>
+      </c>
+      <c r="C302" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Voice Assistant &amp; Community Feed #299</t>
+        </is>
+      </c>
+      <c r="D302" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_299</t>
+        </is>
+      </c>
+      <c r="E302" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F302" s="14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>MOB300</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="inlineStr">
+        <is>
+          <t>Appium Mobile Feature Test #300</t>
+        </is>
+      </c>
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>Verify gesture, touch element &amp; mobile UI navigation for Hardware &amp; Network Resilience #300</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>MobileComponent_300</t>
+        </is>
+      </c>
+      <c r="E303" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F303" s="14" t="n">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
